--- a/Result/profitability/6136.xlsx
+++ b/Result/profitability/6136.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.38</v>
       </c>
       <c r="M2" t="n">
-        <v>0.265</v>
+        <v>0.16375</v>
       </c>
       <c r="N2" t="n">
-        <v>24.33625</v>
+        <v>25.49</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0.2</v>
+        <v>0.18875</v>
       </c>
       <c r="N3" t="n">
-        <v>24.2675</v>
+        <v>25.305</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.19</v>
       </c>
       <c r="M4" t="n">
-        <v>0.33875</v>
+        <v>0.33375</v>
       </c>
       <c r="N4" t="n">
-        <v>24.7225</v>
+        <v>25.01125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>0.18</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3575</v>
+        <v>0.3462499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>24.46875</v>
+        <v>24.08625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.35</v>
       </c>
       <c r="M6" t="n">
-        <v>0.39125</v>
+        <v>0.2862499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>23.36875</v>
+        <v>23.76125</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.28</v>
       </c>
       <c r="M7" t="n">
-        <v>0.3225</v>
+        <v>0.3275</v>
       </c>
       <c r="N7" t="n">
-        <v>23.105</v>
+        <v>24.36625</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>0.44625</v>
+        <v>0.44875</v>
       </c>
       <c r="N8" t="n">
-        <v>23.7225</v>
+        <v>23.595</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>2.09</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7962499999999999</v>
+        <v>0.79625</v>
       </c>
       <c r="N12" t="n">
         <v>27.31125</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6136</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>162</v>
+      </c>
+      <c r="D75" t="n">
+        <v>115</v>
+      </c>
+      <c r="E75" t="n">
+        <v>47</v>
+      </c>
+      <c r="F75" t="n">
+        <v>29.07</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-10</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-6.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>11</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-2</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.01</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.21625</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.44625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.6666666666666666</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.02</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.03389830508474578</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-0.09</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-1.125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-3.060000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.09523809523809534</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
